--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484780_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484780_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2345</v>
+        <v>4.8225</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3157</v>
+        <v>3.1153</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9188</v>
+        <v>1.7071</v>
       </c>
       <c r="G2" t="n">
         <v>5.0791</v>
@@ -610,13 +610,13 @@
         <v>2.4531</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7124</v>
+        <v>-1.1244</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.117</v>
+        <v>-0.3173</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5954</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>1.2452</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LÓPEZ</t>
+          <t>J. GARCIA CORBI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1678</v>
+        <v>2.3984</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1678</v>
+        <v>1.8721</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.5263</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1678</v>
+        <v>2.2695</v>
       </c>
       <c r="H3" t="n">
-        <v>0.317</v>
+        <v>1.3711</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8509</v>
+        <v>0.8983</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1678</v>
+        <v>1.7886</v>
       </c>
       <c r="K3" t="n">
-        <v>0.317</v>
+        <v>1.6481</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8509</v>
+        <v>0.1404</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.4809</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0.277</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.7579</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0.8902</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0.2183</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. GARCIA CORBI</t>
+          <t>J. GONZALEZ LÓPEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6672</v>
+        <v>2.1678</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3261</v>
+        <v>2.1678</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3411</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2695</v>
+        <v>2.1678</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3711</v>
+        <v>0.317</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8983</v>
+        <v>1.8509</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7886</v>
+        <v>2.1678</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6481</v>
+        <v>0.317</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1404</v>
+        <v>1.8509</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4809</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.277</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7579</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3209</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3209</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6213</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7642</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8571</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. DE YRAOLAGOTIA TELLO</t>
+          <t>V. BERENGUER DEL VALLE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0639</v>
+        <v>0.6082</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.5724</v>
+        <v>0.5135</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6363</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.327</v>
+        <v>0.634</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1778</v>
+        <v>0.1816</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5048</v>
+        <v>0.4524</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1295</v>
+        <v>0.71</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7647</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.6352</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4565</v>
+        <v>-0.076</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5869</v>
+        <v>0.097</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1304</v>
+        <v>-0.173</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1322</v>
+        <v>0.7548</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0192</v>
+        <v>0.7548</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2587</v>
+        <v>-0.7996</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1851</v>
+        <v>-0.1965</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0736</v>
+        <v>-0.6031</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. BERENGUER DEL VALLE</t>
+          <t>J. DE YRAOLAGOTIA TELLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4049</v>
+        <v>0.3072</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4161</v>
+        <v>-1.7472</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0111</v>
+        <v>2.0543</v>
       </c>
       <c r="G6" t="n">
-        <v>0.634</v>
+        <v>-0.327</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1816</v>
+        <v>1.1778</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4524</v>
+        <v>-1.5048</v>
       </c>
       <c r="J6" t="n">
-        <v>0.71</v>
+        <v>0.1295</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08450000000000001</v>
+        <v>1.7647</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6254999999999999</v>
+        <v>-1.6352</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.076</v>
+        <v>-0.4565</v>
       </c>
       <c r="N6" t="n">
-        <v>0.097</v>
+        <v>-0.5869</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.173</v>
+        <v>0.1304</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7548</v>
+        <v>3.0192</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0029</v>
+        <v>-0.4981</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2939</v>
+        <v>0.0103</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7089</v>
+        <v>-0.5084</v>
       </c>
       <c r="V6" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. LOPEZ RICO</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1814</v>
+        <v>0.2347</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6885</v>
+        <v>1.0576</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.507</v>
+        <v>-0.8229</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3791</v>
+        <v>0.9583</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8397</v>
+        <v>0.8069</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2189</v>
+        <v>0.1515</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1404</v>
+        <v>2.3727</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0354</v>
+        <v>1.4423</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.1757</v>
+        <v>0.9304</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2388</v>
+        <v>-1.4144</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1956</v>
+        <v>-0.6354</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0431</v>
+        <v>-0.7789</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9435</v>
+        <v>1.5096</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9435</v>
+        <v>2.4531</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-1.007</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8288</v>
+        <v>-0.3716</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.91</v>
+        <v>-0.6354</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3018</v>
+        <v>-1.2262</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3018</v>
+        <v>-1.2262</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>M. LOPEZ RICO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1609</v>
+        <v>-0.2974</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6091</v>
+        <v>0.1039</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.77</v>
+        <v>-0.4012</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9583</v>
+        <v>-0.3791</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8069</v>
+        <v>0.8397</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1515</v>
+        <v>-1.2189</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3727</v>
+        <v>-0.1404</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4423</v>
+        <v>1.0354</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9304</v>
+        <v>-1.1757</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4144</v>
+        <v>-0.2388</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6354</v>
+        <v>-0.1956</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7789</v>
+        <v>-0.0431</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5096</v>
+        <v>0.9435</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4531</v>
+        <v>0.9435</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4026</v>
+        <v>-0.5599</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8201000000000001</v>
+        <v>0.2442</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5825</v>
+        <v>-0.8041</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2262</v>
+        <v>-0.3018</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2262</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.2681</v>
+        <v>-3.8498</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5202</v>
+        <v>-2.2078</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7479</v>
+        <v>-1.642</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8084</v>
@@ -1156,13 +1156,13 @@
         <v>2.2644</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3091</v>
+        <v>-0.8909</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4086</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9005</v>
+        <v>-0.7947</v>
       </c>
       <c r="V9" t="n">
         <v>-2.4714</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6519</v>
+        <v>-4.9842</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1233</v>
+        <v>-0.7466</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.5286</v>
+        <v>-4.2376</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4732</v>
@@ -1234,13 +1234,13 @@
         <v>2.0757</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2734</v>
+        <v>-0.6057</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8317</v>
+        <v>0.2085</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1051</v>
+        <v>-0.8141</v>
       </c>
       <c r="V10" t="n">
         <v>-3.094</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3745</v>
+        <v>-5.5551</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1744</v>
+        <v>-3.4079</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2</v>
+        <v>-2.1471</v>
       </c>
       <c r="G11" t="n">
         <v>-4.9053</v>
@@ -1312,13 +1312,13 @@
         <v>1.6983</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2239</v>
+        <v>-1.4045</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.053</v>
+        <v>-0.2865</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1709</v>
+        <v>-1.118</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,28 +1345,28 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7357</v>
+        <v>-4.1477</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1330000000000009</v>
+        <v>0.7206999999999995</v>
       </c>
       <c r="F12" t="n">
         <v>-4.868399999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>2.215699999999998</v>
+        <v>2.2157</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4852999999999996</v>
+        <v>0.4853000000000005</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7304</v>
+        <v>1.730399999999999</v>
       </c>
       <c r="J12" t="n">
         <v>8.424800000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>5.939700000000001</v>
+        <v>5.939699999999999</v>
       </c>
       <c r="L12" t="n">
         <v>2.4851</v>
@@ -1375,10 +1375,10 @@
         <v>-6.2094</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.454499999999999</v>
+        <v>-5.4545</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7546000000000002</v>
+        <v>-0.7546</v>
       </c>
       <c r="P12" t="n">
         <v>7.548</v>
@@ -1390,13 +1390,13 @@
         <v>16.983</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.368</v>
+        <v>-7.780299999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.6112</v>
+        <v>-1.0234</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.7568</v>
+        <v>-6.7567</v>
       </c>
       <c r="V12" t="n">
         <v>-6.131</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5405</v>
+        <v>5.8773</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8345</v>
+        <v>5.2243</v>
       </c>
       <c r="F13" t="n">
-        <v>0.706</v>
+        <v>0.6531</v>
       </c>
       <c r="G13" t="n">
         <v>5.156</v>
@@ -1468,13 +1468,13 @@
         <v>1.5096</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9888</v>
+        <v>1.3256</v>
       </c>
       <c r="T13" t="n">
-        <v>0.606</v>
+        <v>0.9957</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3828</v>
+        <v>0.3299</v>
       </c>
       <c r="V13" t="n">
         <v>1.8488</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0793</v>
+        <v>2.3003</v>
       </c>
       <c r="E14" t="n">
-        <v>5.1257</v>
+        <v>3.6642</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0464</v>
+        <v>-1.3639</v>
       </c>
       <c r="G14" t="n">
         <v>-0.09660000000000001</v>
@@ -1546,13 +1546,13 @@
         <v>1.3209</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8933</v>
+        <v>2.1143</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3218</v>
+        <v>1.8603</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5715</v>
+        <v>0.254</v>
       </c>
       <c r="V14" t="n">
         <v>2.1696</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5072</v>
+        <v>2.0292</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5933</v>
+        <v>1.983</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0861</v>
+        <v>0.0462</v>
       </c>
       <c r="G15" t="n">
         <v>1.1274</v>
@@ -1624,13 +1624,13 @@
         <v>0.7548</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6202</v>
+        <v>-0.0982</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3527</v>
+        <v>0.037</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2674</v>
+        <v>-0.1352</v>
       </c>
       <c r="V15" t="n">
         <v>0.6226</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. SIDDIQUE</t>
+          <t>D. CAZORLA ZARAGOZI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6838</v>
+        <v>0.9528</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0701</v>
+        <v>0.7687</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6137</v>
+        <v>0.1841</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1665</v>
+        <v>0.2238</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7601</v>
+        <v>-0.8937</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5936</v>
+        <v>1.1176</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3601</v>
+        <v>1.5288</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.109</v>
+        <v>-0.4539</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7489</v>
+        <v>1.9828</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1936</v>
+        <v>-1.305</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6511</v>
+        <v>-0.4398</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8447</v>
+        <v>-0.8652</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5661</v>
+        <v>0.1887</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1322</v>
+        <v>-1.3209</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5661</v>
+        <v>1.5096</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1146</v>
+        <v>0.5592</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9587</v>
+        <v>0.5797</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1558</v>
+        <v>-0.0205</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3018</v>
+        <v>-0.019</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6036</v>
+        <v>-0.019</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>U. ZAMORA MAÑA</t>
+          <t>S. SIDDIQUE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.617</v>
+        <v>0.8244</v>
       </c>
       <c r="E17" t="n">
-        <v>0.617</v>
+        <v>-0.0274</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.8518</v>
       </c>
       <c r="G17" t="n">
-        <v>0.617</v>
+        <v>-0.1665</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-1.7601</v>
       </c>
       <c r="I17" t="n">
-        <v>0.617</v>
+        <v>1.5936</v>
       </c>
       <c r="J17" t="n">
-        <v>0.617</v>
+        <v>-0.3601</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-1.109</v>
       </c>
       <c r="L17" t="n">
-        <v>0.617</v>
+        <v>0.7489</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.1936</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.6511</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.8447</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.2552</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.8613</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.3939</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>U. ZAMORA MANA</t>
+          <t>U. ZAMORA MAÑA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0364</v>
+        <v>0.617</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5667</v>
+        <v>0.617</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6031</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.9869</v>
+        <v>0.617</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1404</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.8465</v>
+        <v>0.617</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.8097</v>
+        <v>0.617</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0667</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.743</v>
+        <v>0.617</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1772</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0737</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1035</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.3209</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6983</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.0827</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9051</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1776</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>2.4904</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7922</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. CAZORLA ZARAGOZI</t>
+          <t>J. ORTOLA TOMAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0732</v>
+        <v>-0.0125</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0866</v>
+        <v>-1.1233</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1598</v>
+        <v>1.1108</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2238</v>
+        <v>-0.5129</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8937</v>
+        <v>-0.4437</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1176</v>
+        <v>-0.0692</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5288</v>
+        <v>-0.8154</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4539</v>
+        <v>-0.2481</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9828</v>
+        <v>-0.5673</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.305</v>
+        <v>0.3024</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4398</v>
+        <v>-0.1956</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8652</v>
+        <v>0.4981</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1887</v>
+        <v>0.3774</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3209</v>
+        <v>-0.1887</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5096</v>
+        <v>0.5661</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4667</v>
+        <v>0.123</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1023</v>
+        <v>-0.1192</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3644</v>
+        <v>0.2422</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.019</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.019</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. ORTOLA TOMAS</t>
+          <t>U. ZAMORA MANA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1196</v>
+        <v>-0.9397</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4156</v>
+        <v>-0.3102</v>
       </c>
       <c r="F20" t="n">
-        <v>1.296</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5129</v>
+        <v>-4.9869</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4437</v>
+        <v>-2.1404</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0692</v>
+        <v>-2.8465</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8154</v>
+        <v>-2.8097</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2481</v>
+        <v>-1.0667</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5673</v>
+        <v>-1.743</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3024</v>
+        <v>-2.1772</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1956</v>
+        <v>-1.0737</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4981</v>
+        <v>-1.1035</v>
       </c>
       <c r="P20" t="n">
         <v>0.3774</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1887</v>
+        <v>-1.3209</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5661</v>
+        <v>1.6983</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0159</v>
+        <v>1.1794</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4115</v>
+        <v>1.0282</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4274</v>
+        <v>0.1512</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2.4904</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.7922</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5514</v>
+        <v>-2.7101</v>
       </c>
       <c r="E21" t="n">
         <v>-4.8502</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2988</v>
+        <v>2.1401</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0272</v>
@@ -2092,13 +2092,13 @@
         <v>0.3774</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4009</v>
+        <v>1.2422</v>
       </c>
       <c r="T21" t="n">
         <v>0.8875999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5133</v>
+        <v>0.3545</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3398</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9116</v>
+        <v>-4.2031</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7596</v>
+        <v>-1.0776</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1519</v>
+        <v>-3.1255</v>
       </c>
       <c r="G22" t="n">
         <v>-3.5496</v>
@@ -2170,13 +2170,13 @@
         <v>1.1322</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0412</v>
+        <v>0.6673</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0559</v>
+        <v>0.6261</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0147</v>
+        <v>0.0412</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9434</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.735600000000002</v>
+        <v>4.735599999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>4.868499999999999</v>
+        <v>4.868500000000001</v>
       </c>
       <c r="F23" t="n">
         <v>-0.1328</v>
@@ -2215,7 +2215,7 @@
         <v>-2.2155</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4852000000000001</v>
+        <v>-0.485200000000001</v>
       </c>
       <c r="I23" t="n">
         <v>-1.7302</v>
@@ -2224,7 +2224,7 @@
         <v>6.2094</v>
       </c>
       <c r="K23" t="n">
-        <v>5.4545</v>
+        <v>5.454499999999999</v>
       </c>
       <c r="L23" t="n">
         <v>0.7548999999999995</v>
@@ -2239,7 +2239,7 @@
         <v>-2.4852</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.547999999999999</v>
+        <v>-7.548</v>
       </c>
       <c r="Q23" t="n">
         <v>-16.983</v>
@@ -2248,13 +2248,13 @@
         <v>9.434999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>8.3681</v>
+        <v>8.367999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>6.7568</v>
+        <v>6.756699999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>1.6113</v>
+        <v>1.6112</v>
       </c>
       <c r="V23" t="n">
         <v>6.131</v>
